--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/UsingTables.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/UsingTables.xlsx
@@ -888,9 +888,9 @@
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed"/>
   <x:headerFooter/>
   <x:tableParts count="3">
-    <x:tablePart r:id="rId1"/>
-    <x:tablePart r:id="rId5"/>
     <x:tablePart r:id="rId7"/>
+    <x:tablePart r:id="rId8"/>
+    <x:tablePart r:id="rId10"/>
   </x:tableParts>
 </x:worksheet>
 </file>
--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/UsingTables.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/UsingTables.xlsx
@@ -75,7 +75,7 @@
     <x:numFmt numFmtId="0" formatCode=""/>
     <x:numFmt numFmtId="1" formatCode="$ #,##0"/>
   </x:numFmts>
-  <x:fonts count="2">
+  <x:fonts count="4">
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
@@ -85,6 +85,20 @@
     </x:font>
     <x:font>
       <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="11"/>
+      <x:color rgb="FF000000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
       <x:color rgb="FF000000"/>
@@ -284,7 +298,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="17">
+  <x:cellStyleXfs count="19">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -330,6 +344,12 @@
     <x:xf numFmtId="1" fontId="0" fillId="0" borderId="9" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="15" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="15" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -337,7 +357,7 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="17">
+  <x:cellXfs count="19">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -395,6 +415,14 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="1" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="15" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -760,10 +788,10 @@
       <x:c r="D2" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="E2" s="15" t="s">
+      <x:c r="E2" s="17" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="F2" s="16" t="s">
+      <x:c r="F2" s="18" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="G2" s="0" t="s"/>
@@ -785,10 +813,10 @@
       <x:c r="D3" s="0" t="b">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="E3" s="15">
+      <x:c r="E3" s="17">
         <x:v>6961</x:v>
       </x:c>
-      <x:c r="F3" s="16" t="n">
+      <x:c r="F3" s="18" t="n">
         <x:v>2000</x:v>
       </x:c>
       <x:c r="G3" s="0" t="s"/>
@@ -810,10 +838,10 @@
       <x:c r="D4" s="0" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E4" s="15">
+      <x:c r="E4" s="17">
         <x:v>2620</x:v>
       </x:c>
-      <x:c r="F4" s="16" t="n">
+      <x:c r="F4" s="18" t="n">
         <x:v>40000</x:v>
       </x:c>
       <x:c r="G4" s="0" t="s"/>
@@ -835,10 +863,10 @@
       <x:c r="D5" s="0" t="b">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="E5" s="15">
+      <x:c r="E5" s="17">
         <x:v>8020</x:v>
       </x:c>
-      <x:c r="F5" s="16" t="n">
+      <x:c r="F5" s="18" t="n">
         <x:v>10000</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s"/>
@@ -856,8 +884,8 @@
       </x:c>
       <x:c r="C6" s="0" t="s"/>
       <x:c r="D6" s="0" t="s"/>
-      <x:c r="E6" s="15" t="s"/>
-      <x:c r="F6" s="16" t="n">
+      <x:c r="E6" s="17" t="s"/>
+      <x:c r="F6" s="18" t="n">
         <x:f>SUBTOTAL(109,[Income])</x:f>
       </x:c>
       <x:c r="G6" s="0" t="s"/>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/UsingTables.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/UsingTables.xlsx
@@ -767,15 +767,15 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="3.710625" style="0" customWidth="1"/>
-    <x:col min="2" max="2" width="16.410625" style="0" customWidth="1"/>
-    <x:col min="3" max="3" width="10.410625" style="0" customWidth="1"/>
-    <x:col min="4" max="4" width="9.700625" style="0" customWidth="1"/>
-    <x:col min="5" max="5" width="11.270625" style="0" customWidth="1"/>
-    <x:col min="6" max="6" width="9.550625" style="0" customWidth="1"/>
+    <x:col min="2" max="2" width="14.890625" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="9.000625" style="0" customWidth="1"/>
+    <x:col min="4" max="4" width="8.440625" style="0" customWidth="1"/>
+    <x:col min="5" max="5" width="10.140625" style="0" customWidth="1"/>
+    <x:col min="6" max="6" width="9.210625" style="0" customWidth="1"/>
     <x:col min="7" max="7" width="3.710625" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="15.410625" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14.010625000000001" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="3.710625" style="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15.270625" style="0" customWidth="1"/>
+    <x:col min="10" max="10" width="13.830625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="2" spans="1:10">

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/UsingTables.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/UsingTables.xlsx
@@ -344,10 +344,10 @@
     <x:xf numFmtId="1" fontId="0" fillId="0" borderId="9" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="15" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="15" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
@@ -418,11 +418,11 @@
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="15" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/UsingTables.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/UsingTables.xlsx
@@ -344,10 +344,10 @@
     <x:xf numFmtId="1" fontId="0" fillId="0" borderId="9" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="15" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="15" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="15" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
@@ -418,11 +418,11 @@
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="15" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
     <x:xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="15" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/UsingTables.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/UsingTables.xlsx
@@ -299,138 +299,138 @@
     </x:border>
   </x:borders>
   <x:cellStyleXfs count="19">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="4" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="5" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="6" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="15" fontId="0" fillId="0" borderId="5" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="6" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="15" fontId="0" fillId="0" borderId="8" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="9" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="15" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="15" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="4" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="5" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="6" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="15" fontId="0" fillId="0" borderId="5" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="15" fontId="0" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="15" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="15" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
   <x:cellXfs count="19">
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="0" applyFill="0" applyBorder="1" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="1" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="15" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="15" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="1" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="15" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
-      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <x:protection locked="1" hidden="0"/>
-    </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="0" applyFill="1" applyBorder="0" applyAlignment="0" applyProtection="1">
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="15" fontId="0" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="15" fontId="0" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="15" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="15" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/UsingTables.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/UsingTables.xlsx
@@ -773,7 +773,7 @@
     <x:col min="5" max="5" width="10.140625" style="0" customWidth="1"/>
     <x:col min="6" max="6" width="9.210625" style="0" customWidth="1"/>
     <x:col min="7" max="7" width="3.710625" style="0" customWidth="1"/>
-    <x:col min="8" max="8" width="14.010625000000001" style="0" customWidth="1"/>
+    <x:col min="8" max="8" width="14.010625" style="0" customWidth="1"/>
     <x:col min="9" max="9" width="3.710625" style="0" customWidth="1"/>
     <x:col min="10" max="10" width="13.830625" style="0" customWidth="1"/>
   </x:cols>
@@ -794,11 +794,9 @@
       <x:c r="F2" s="18" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="G2" s="0" t="s"/>
       <x:c r="H2" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="I2" s="0" t="s"/>
       <x:c r="J2" s="0" t="s">
         <x:v>6</x:v>
       </x:c>
@@ -819,11 +817,9 @@
       <x:c r="F3" s="18" t="n">
         <x:v>2000</x:v>
       </x:c>
-      <x:c r="G3" s="0" t="s"/>
       <x:c r="H3" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="I3" s="0" t="s"/>
       <x:c r="J3" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
@@ -844,11 +840,9 @@
       <x:c r="F4" s="18" t="n">
         <x:v>40000</x:v>
       </x:c>
-      <x:c r="G4" s="0" t="s"/>
       <x:c r="H4" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I4" s="0" t="s"/>
       <x:c r="J4" s="0" t="s">
         <x:v>12</x:v>
       </x:c>
@@ -869,11 +863,9 @@
       <x:c r="F5" s="18" t="n">
         <x:v>10000</x:v>
       </x:c>
-      <x:c r="G5" s="0" t="s"/>
       <x:c r="H5" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
-      <x:c r="I5" s="0" t="s"/>
       <x:c r="J5" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
@@ -882,25 +874,15 @@
       <x:c r="B6" s="0" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="C6" s="0" t="s"/>
-      <x:c r="D6" s="0" t="s"/>
       <x:c r="E6" s="17" t="s"/>
       <x:c r="F6" s="18" t="n">
         <x:f>SUBTOTAL(109,[Income])</x:f>
       </x:c>
-      <x:c r="G6" s="0" t="s"/>
       <x:c r="H6" s="0" t="s">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="I6" s="0" t="s"/>
-      <x:c r="J6" s="0" t="s"/>
     </x:row>
     <x:row r="7" spans="1:10">
-      <x:c r="B7" s="0" t="s"/>
-      <x:c r="C7" s="0" t="s"/>
-      <x:c r="D7" s="0" t="s"/>
-      <x:c r="E7" s="0" t="s"/>
-      <x:c r="F7" s="0" t="s"/>
       <x:c r="H7" s="0" t="s">
         <x:v>4</x:v>
       </x:c>

--- a/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/UsingTables.xlsx
+++ b/ClosedXML/ClosedXML/ClosedXML_Tests/Resource/Examples/Ranges/UsingTables.xlsx
@@ -73,7 +73,7 @@
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:numFmts count="2">
     <x:numFmt numFmtId="0" formatCode=""/>
-    <x:numFmt numFmtId="1" formatCode="$ #,##0"/>
+    <x:numFmt numFmtId="165" formatCode="$ #,##0"/>
   </x:numFmts>
   <x:fonts count="4">
     <x:font>
@@ -329,7 +329,7 @@
     <x:xf numFmtId="15" fontId="0" fillId="0" borderId="5" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="6" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="7" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -341,19 +341,19 @@
     <x:xf numFmtId="15" fontId="0" fillId="0" borderId="8" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="9" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="15" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="1" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="2" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="15" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
   </x:cellStyleXfs>
@@ -398,7 +398,7 @@
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -414,7 +414,7 @@
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -422,7 +422,7 @@
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -430,7 +430,7 @@
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
-    <x:xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
+    <x:xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
